--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488287_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488287_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0731</v>
+        <v>10.9947</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3681</v>
+        <v>8.486700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.705</v>
+        <v>2.508</v>
       </c>
       <c r="G2" t="n">
         <v>4.1108</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2986</v>
+        <v>1.2202</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7397</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5588</v>
+        <v>0.3619</v>
       </c>
       <c r="V2" t="n">
         <v>5.6637</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.647600000000001</v>
+        <v>8.9922</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4433</v>
+        <v>6.7797</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2043</v>
+        <v>2.2125</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0172</v>
+        <v>7.5765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5101</v>
+        <v>0.8873</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5071</v>
+        <v>6.6892</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0094</v>
+        <v>7.1522</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1979</v>
+        <v>0.7857</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2074</v>
+        <v>6.3665</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0077</v>
+        <v>0.4243</v>
       </c>
       <c r="N3" t="n">
-        <v>0.708</v>
+        <v>0.1016</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2997</v>
+        <v>0.3227</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6691</v>
+        <v>0.0631</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9549</v>
+        <v>-0.0575</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7143</v>
+        <v>0.1206</v>
       </c>
       <c r="V3" t="n">
-        <v>4.4054</v>
+        <v>-0.315</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4054</v>
+        <v>-0.315</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.281000000000001</v>
+        <v>7.1775</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2901</v>
+        <v>4.1702</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9909</v>
+        <v>3.0073</v>
       </c>
       <c r="G4" t="n">
-        <v>7.5765</v>
+        <v>1.0172</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8873</v>
+        <v>0.5101</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6892</v>
+        <v>0.5071</v>
       </c>
       <c r="J4" t="n">
-        <v>7.1522</v>
+        <v>0.0094</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7857</v>
+        <v>-0.1979</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3665</v>
+        <v>0.2074</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4243</v>
+        <v>1.0077</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1016</v>
+        <v>0.708</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3227</v>
+        <v>0.2997</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6481</v>
+        <v>1.1991</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5471</v>
+        <v>0.6818</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.101</v>
+        <v>0.5173</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.315</v>
+        <v>4.4054</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.315</v>
+        <v>4.4054</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.784</v>
+        <v>6.5148</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9538</v>
+        <v>3.66</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8302</v>
+        <v>2.8548</v>
       </c>
       <c r="G5" t="n">
         <v>3.9248</v>
@@ -844,13 +844,13 @@
         <v>2.594</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1916</v>
+        <v>0.9224</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.4648</v>
       </c>
       <c r="U5" t="n">
-        <v>0.433</v>
+        <v>0.4576</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.139</v>
+        <v>2.3108</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5576</v>
+        <v>-0.4596</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6966</v>
+        <v>2.7704</v>
       </c>
       <c r="G6" t="n">
         <v>0.978</v>
@@ -922,13 +922,13 @@
         <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2345</v>
+        <v>0.4063</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1604</v>
+        <v>0.2584</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0741</v>
+        <v>0.148</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1358</v>
+        <v>1.5499</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4924</v>
+        <v>-1.709</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6283</v>
+        <v>3.2589</v>
       </c>
       <c r="G8" t="n">
         <v>0.2206</v>
@@ -1078,13 +1078,13 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5446</v>
+        <v>0.9588</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6019</v>
+        <v>0.1816</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1465</v>
+        <v>0.7772</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1218</v>
+        <v>1.1951</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0903</v>
+        <v>-0.9923</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2121</v>
+        <v>2.1874</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8829</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>1.487</v>
+        <v>1.5603</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8133</v>
+        <v>0.9112</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6737</v>
+        <v>0.6491</v>
       </c>
       <c r="V9" t="n">
         <v>1.8883</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3632</v>
+        <v>0.9754</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0518</v>
+        <v>0.5357</v>
       </c>
       <c r="F10" t="n">
-        <v>0.415</v>
+        <v>0.4396</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5235</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0164</v>
+        <v>0.6286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>0.314</v>
       </c>
       <c r="U10" t="n">
-        <v>0.29</v>
+        <v>0.3146</v>
       </c>
       <c r="V10" t="n">
         <v>0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1755</v>
+        <v>0.12</v>
       </c>
       <c r="E12" t="n">
         <v>-3.7843</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6089</v>
+        <v>3.9043</v>
       </c>
       <c r="G12" t="n">
         <v>0.8064</v>
@@ -1390,13 +1390,13 @@
         <v>2.0382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2407</v>
+        <v>0.0547</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0584</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1823</v>
+        <v>0.1131</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3246</v>
+        <v>-1.5653</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0609</v>
+        <v>-1.3754</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2638</v>
+        <v>-0.1899</v>
       </c>
       <c r="G13" t="n">
         <v>-1.58</v>
@@ -1468,13 +1468,13 @@
         <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2455</v>
+        <v>0.5139</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4377</v>
+        <v>0.2478</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1922</v>
+        <v>0.2661</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3139</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.6984</v>
+        <v>-2.9184</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2337</v>
+        <v>-2.5275</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4647</v>
+        <v>-0.3909</v>
       </c>
       <c r="G14" t="n">
         <v>-2.1261</v>
@@ -1546,13 +1546,13 @@
         <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4832</v>
+        <v>0.2633</v>
       </c>
       <c r="T14" t="n">
-        <v>0.434</v>
+        <v>0.1402</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>37.2574</v>
+        <v>37.25709999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>14.6947</v>
+        <v>14.6946</v>
       </c>
       <c r="F15" t="n">
-        <v>22.5628</v>
+        <v>22.5624</v>
       </c>
       <c r="G15" t="n">
         <v>14.4322</v>
@@ -1594,7 +1594,7 @@
         <v>4.947299999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>9.485099999999999</v>
+        <v>9.485100000000001</v>
       </c>
       <c r="J15" t="n">
         <v>12.9891</v>
@@ -1627,10 +1627,10 @@
         <v>7.7907</v>
       </c>
       <c r="T15" t="n">
-        <v>3.942200000000001</v>
+        <v>3.9423</v>
       </c>
       <c r="U15" t="n">
-        <v>3.8485</v>
+        <v>3.8486</v>
       </c>
       <c r="V15" t="n">
         <v>11.3285</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0832</v>
+        <v>0.0339</v>
       </c>
       <c r="E16" t="n">
         <v>0.4574</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3743</v>
+        <v>-0.4235</v>
       </c>
       <c r="G16" t="n">
         <v>-0.012</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1321</v>
+        <v>-1.1814</v>
       </c>
       <c r="T16" t="n">
         <v>-0.6019</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5303</v>
+        <v>-0.5795</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4403</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4263</v>
+        <v>-0.5001</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5766</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1503</v>
+        <v>1.0765</v>
       </c>
       <c r="G18" t="n">
         <v>0.2234</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3527</v>
+        <v>-0.4265</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3283</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0244</v>
+        <v>-0.0982</v>
       </c>
       <c r="V18" t="n">
         <v>0.6294</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.836</v>
+        <v>-0.6407</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3451</v>
+        <v>0.6388</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1811</v>
+        <v>-1.2795</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2292</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3479</v>
+        <v>-0.1526</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4377</v>
+        <v>-0.1439</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0898</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6294</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0546</v>
+        <v>-1.8335</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1412</v>
+        <v>-2.0433</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0867</v>
+        <v>0.2098</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1008</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7685</v>
+        <v>-0.5475</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4402</v>
+        <v>-0.3171</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0283</v>
+        <v>-3.054</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.397</v>
+        <v>-0.2012</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6313</v>
+        <v>-2.8529</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0761</v>
@@ -2092,13 +2092,13 @@
         <v>2.2234</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6029</v>
+        <v>-0.6286</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.766</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1631</v>
+        <v>-0.0585</v>
       </c>
       <c r="V21" t="n">
         <v>-3.461</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4244</v>
+        <v>-3.8105</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0711</v>
+        <v>-0.6112</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3532</v>
+        <v>-3.1992</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3337</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.578</v>
+        <v>-0.7248</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2443</v>
+        <v>-0.2414</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0613</v>
+        <v>0.1442</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3563</v>
+        <v>0.163</v>
       </c>
       <c r="L22" t="n">
-        <v>0.705</v>
+        <v>-0.0189</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.395</v>
+        <v>-1.1104</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9343</v>
+        <v>-0.8878</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4607</v>
+        <v>-0.2226</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1499</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.891</v>
+        <v>-0.1853</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>1.003</v>
+        <v>-0.8126</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7586000000000001</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2445</v>
+        <v>-0.2425</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9439</v>
+        <v>-2.958</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9439</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2525</v>
+        <v>-4.4053</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8071</v>
+        <v>-2.7567</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4454</v>
+        <v>-1.6487</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.3337</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7248</v>
+        <v>-0.578</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2414</v>
+        <v>0.2443</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1442</v>
+        <v>1.0613</v>
       </c>
       <c r="K23" t="n">
-        <v>0.163</v>
+        <v>0.3563</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0189</v>
+        <v>0.705</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1104</v>
+        <v>-1.395</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8878</v>
+        <v>-0.9343</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2226</v>
+        <v>-0.4607</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9264</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1853</v>
+        <v>-3.891</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2547</v>
+        <v>0.0221</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.766</v>
+        <v>0.0731</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4887</v>
+        <v>-0.051</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.958</v>
+        <v>-0.9439</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.958</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0533</v>
+        <v>-5.7388</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6276</v>
+        <v>-5.3131</v>
       </c>
       <c r="F24" t="n">
         <v>-0.4257</v>
@@ -2326,10 +2326,10 @@
         <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5347</v>
+        <v>-1.2202</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2114</v>
+        <v>-0.4741</v>
       </c>
       <c r="U24" t="n">
         <v>-0.7461</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8753</v>
+        <v>-6.7275</v>
       </c>
       <c r="E25" t="n">
         <v>-5.3458</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5295</v>
+        <v>-1.3818</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1471</v>
@@ -2404,13 +2404,13 @@
         <v>1.8529</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.211</v>
+        <v>-1.0632</v>
       </c>
       <c r="T25" t="n">
         <v>-0.2773</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9337</v>
+        <v>-0.7859</v>
       </c>
       <c r="V25" t="n">
         <v>0.1886</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.5471</v>
+        <v>-10.0815</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.9789</v>
+        <v>-5.5872</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.5682</v>
+        <v>-4.4943</v>
       </c>
       <c r="G26" t="n">
         <v>-5.2478</v>
@@ -2482,13 +2482,13 @@
         <v>1.297</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4878</v>
+        <v>-1.0222</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.766</v>
+        <v>-0.3743</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7218</v>
+        <v>-0.6479</v>
       </c>
       <c r="V26" t="n">
         <v>-2.3292</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-36.7067</v>
+        <v>-37.0501</v>
       </c>
       <c r="E27" t="n">
-        <v>-22.176</v>
+        <v>-22.3721</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.5306</v>
+        <v>-14.6782</v>
       </c>
       <c r="G27" t="n">
         <v>-14.0019</v>
@@ -2560,13 +2560,13 @@
         <v>13.8964</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.744</v>
+        <v>-7.0874</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.3562</v>
+        <v>-3.552</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.3878</v>
+        <v>-3.5354</v>
       </c>
       <c r="V27" t="n">
         <v>-11.3285</v>
